--- a/sheets/대금율보/검수/사설시조 (남창).xlsx
+++ b/sheets/대금율보/검수/사설시조 (남창).xlsx
@@ -4431,8 +4431,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–ㄱ
-‹</t>
+–ㄱ</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -4444,8 +4443,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–ㄴ
-‹</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -4471,8 +4469,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -4679,8 +4676,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4692,8 +4688,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -4705,8 +4700,7 @@
         <is>
           <t xml:space="preserve">黃ʊ
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -4742,8 +4736,7 @@
         <is>
           <t xml:space="preserve">–
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="O10" s="22" t="inlineStr">
@@ -4755,8 +4748,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="Q10" s="22" t="inlineStr">
@@ -4854,8 +4846,7 @@
         <is>
           <t xml:space="preserve">林⌇
 –
-–И
-‹</t>
+–И</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -4867,8 +4858,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-太
-‹</t>
+太</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4876,8 +4866,7 @@
         <is>
           <t xml:space="preserve">仲
 –
-–ㄴ
-‹</t>
+–ㄴ</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -4889,8 +4878,7 @@
         <is>
           <t xml:space="preserve">仲
 –ㄴ
-林И
-‹</t>
+林И</t>
         </is>
       </c>
       <c r="K12" s="22" t="inlineStr">
@@ -4902,8 +4890,7 @@
         <is>
           <t xml:space="preserve">–⌇
 –
-太
-‹</t>
+太</t>
         </is>
       </c>
       <c r="M12" s="22"/>

--- a/sheets/대금율보/검수/사설시조 (남창).xlsx
+++ b/sheets/대금율보/검수/사설시조 (남창).xlsx
@@ -4045,30 +4045,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4093,7 +4093,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="141.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="141.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="141.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="141.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="141.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="141.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="141.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4668,7 +4668,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="141.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4759,7 +4759,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="141.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4838,7 +4838,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="141.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4921,7 +4921,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="141.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -5004,7 +5004,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="141.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -5081,7 +5081,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="141.22" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5166,6 +5166,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>